--- a/data/credit_bond_all_2026-10-21.xlsx
+++ b/data/credit_bond_all_2026-10-21.xlsx
@@ -933,8 +933,12 @@
           <t>1.60 ~ 2.20</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>35.43</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.81</t>
@@ -1165,8 +1169,12 @@
           <t>1.30 ~ 1.44</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>23.0</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -1395,8 +1403,12 @@
           <t>1.30 ~ 1.50</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>19.41</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -1625,8 +1637,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>20.41</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -1857,8 +1873,12 @@
           <t>2.20 ~ 3.00</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>96.88</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2.65</t>
@@ -2087,8 +2107,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>92.43</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>2.45</t>
@@ -2337,7 +2361,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2535,8 +2559,12 @@
           <t>1.50 ~ 1.90</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>41.47</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.78</t>
@@ -2767,8 +2795,12 @@
           <t>1.60 ~ 1.91</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>55.43</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
@@ -2824,7 +2856,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="4" t="n">
+        <v>0.81</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -2964,7 +2998,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26海南农垦SCP002</t>
+          <t>26鲁招金MTN001(并购)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2974,12 +3008,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>012682503.IB</t>
+          <t>102684167.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -2990,44 +3024,48 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.42 ~ 1.72</t>
-        </is>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>19.43</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>22海垦01</t>
+          <t>25山招K1</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>264D</t>
+          <t>4.10Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.4950</t>
+          <t>1.6096</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.4900</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>海南省农垦投资控股集团有限公司</t>
+          <t>山东招金集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.98</t>
+          <t>B- 41.32</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3042,7 +3080,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3051,19 +3089,19 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.72</v>
+        <v>2.93</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.75</v>
+        <v>6.0</v>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3074,23 +3112,23 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>海南省-海口市</t>
+          <t>山东省-烟台市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期拟发行10亿元人民币,8.4亿元用于归还发行人到期债务,1.6亿元用于补充母公司或子公司流动资金。</t>
+          <t>本期中期票据发行规模为10亿元,全部用于偿还发行人即将到期的银行贷款</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国建设银行股份有限公司,招商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3105,7 +3143,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>海南省农垦投资控股集团有限公司2026年度第二期超短期融资券</t>
+          <t>山东招金集团有限公司2026年度第一期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3115,7 +3153,7 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2027-07-19</t>
+          <t>2031-10-22</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3141,27 +3179,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>贵金属</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3196,7 +3234,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26鲁招金MTN001(并购)</t>
+          <t>26中建六局SCP002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3206,60 +3244,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102684167.IB</t>
+          <t>012682506.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>1.30 ~ 1.59</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>20.96</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25山招K1</t>
+          <t>26中建六局SCP001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.10Y</t>
+          <t>261D</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.6096</t>
+          <t>1.4786</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>1.4800/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>山东招金集团有限公司</t>
+          <t>中国建筑第六工程局有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 41.32</t>
+          <t>B- 42.56</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3269,12 +3311,12 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-21 10:00</t>
+          <t>10-21 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3283,19 +3325,19 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>6.0</v>
+        <v>1.2</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3306,28 +3348,28 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>山东省-烟台市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为10亿元,全部用于偿还发行人即将到期的银行贷款</t>
+          <t>本期超短期融资券发行金额6亿元。本期超短期融资券全部募集资金拟用于偿还有息负债(流动资金贷款)</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>渤海银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
@@ -3337,7 +3379,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>山东招金集团有限公司2026年度第一期中期票据(并购)</t>
+          <t>中国建筑第六工程局有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3347,7 +3389,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-10-22</t>
+          <t>2027-07-19</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3373,27 +3415,27 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>贵金属</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3428,72 +3470,58 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26中建六局SCP002</t>
+          <t>航亚转债</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>10-21 18:00</t>
+          <t>10-21 15:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>012682506.IB</t>
+          <t>118078.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>1.30 ~ 1.59</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>-130.48</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>26中建六局SCP001</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>261D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.4786</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.4800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>B- 42.56</t>
-        </is>
-      </c>
+          <t>无锡航亚科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P15" s="3"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -3501,75 +3529,71 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-21 09:00</t>
+          <t>10-21 09:30</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>1.2</v>
-      </c>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>1.46%~1.50%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X15" s="3"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z15" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元。本期超短期融资券全部募集资金拟用于偿还有息负债(流动资金贷款)</t>
+          <t>公司拟向不特定对象发行可转换公司债券的募集资金总额不超过人民币60,000.00万元(含本数),扣除发行费用后,拟用于航空叶片与医疗骨科植入锻件马来西亚智能制造基地项目、航空发动机转动件和结构件产能扩建项目、补充流动资金项目</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,华夏银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司2026年度第二期超短期融资券</t>
+          <t>2026年无锡航亚科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3579,53 +3603,49 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2027-07-19</t>
+          <t>2032-10-21</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP15" s="3"/>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>交运设备制造</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>其他交运设备</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>其他交运设备</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>航空装备</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3653,127 +3673,141 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>航亚转债</t>
+          <t>26平凉02</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>10-21 19:00</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>284212.SH</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>26平凉01</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>4.39Y</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>2.2784</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>平凉市城乡发展建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>C 30.00</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
           <t>10-21 15:00</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>118078.SH</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>6Y</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>-130.48</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="S16" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>无锡航亚科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>10-21 09:30</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X16" s="3"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>2.60%~2.70%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+      <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>甘肃省-平凉市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>公司拟向不特定对象发行可转换公司债券的募集资金总额不超过人民币60,000.00万元(含本数),扣除发行费用后,拟用于航空叶片与医疗骨科植入锻件马来西亚智能制造基地项目、航空发动机转动件和结构件产能扩建项目、补充流动资金项目</t>
+          <t>本期债券发行规模4.00亿元,扣除发行费用以后,仅用于偿还“24平凉01”债券本金。[24平凉01]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>华龙证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3783,59 +3817,63 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>2026年无锡航亚科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>平凉市城乡发展建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2032-10-21</t>
+          <t>2031-10-22</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>交运设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>其他交运设备</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他交运设备</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>航空装备</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3868,7 +3906,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26平凉02</t>
+          <t>26武空01</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3878,47 +3916,47 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>284212.SH</t>
+          <t>284296.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>104.43</v>
+        <v>18.88</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26平凉01</t>
+          <t>25武空05</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.39Y</t>
+          <t>3.88Y+5.00Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.2784</t>
+          <t>1.8149</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3928,12 +3966,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>平凉市城乡发展建设投资集团有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>B- 35.98</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3953,40 +3991,42 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="U17" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>2.79</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.60%~2.70%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-平凉市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模4.00亿元,扣除发行费用以后,仅用于偿还“24平凉01”债券本金。[24平凉01]</t>
+          <t>本期债券发行总额不超过15.00亿元(含15.00亿元)本期公司债券募集资金拟用于偿还到期公司债券的本金[23武空02]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>华龙证券股份有限公司</t>
+          <t>国金证券股份有限公司,申港证券股份有限公司,中天国富证券有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4007,7 +4047,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>平凉市城乡发展建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>武汉临空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4017,13 +4057,17 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-10-22</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2036-10-26</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t/>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
@@ -4033,32 +4077,32 @@
       </c>
       <c r="AN17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
@@ -4068,7 +4112,7 @@
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-26</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4078,7 +4122,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4096,68 +4140,68 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26武空01</t>
+          <t>26湖州产投PPN002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>10-21 19:00</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>284296.SH</t>
-        </is>
-      </c>
+          <t>10-21 18:00</t>
+        </is>
+      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+          <t>1.45 ~ 2.15</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>33.43</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>25武空05</t>
+          <t>26湖产03</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.88Y+5.00Y</t>
+          <t>2.92Y+2.00Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.8149</t>
+          <t>1.7227</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/1.6800</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>湖州市产业投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 35.98</t>
+          <t>C 26.74</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4167,56 +4211,58 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-21 15:00</t>
+          <t>10-21 09:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="U18" s="3"/>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>2.7</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过15.00亿元(含15.00亿元)本期公司债券募集资金拟用于偿还到期公司债券的本金[23武空02]</t>
+          <t>发行人本期定向债务融资工具发行拟募集资金5亿元,所募集资金拟用于偿还接续“25湖州产投SCP006”本金的过桥贷款[25湖州产投SCP006]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,申港证券股份有限公司,中天国富证券有限公司</t>
+          <t>国投证券股份有限公司,江苏银行股份有限公司,东方证券股份有限公司,杭州银行股份有限公司,中信建投证券股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4226,12 +4272,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>湖州市产业投资发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4241,62 +4287,58 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2036-10-26</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-22</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t>2031-10-26</t>
+          <t>2029-10-22</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4324,7 +4366,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26湖州产投PPN002</t>
+          <t>26凯利建设PPN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4335,53 +4377,57 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 2.15</t>
-        </is>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+          <t>2.20 ~ 3.20</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>132.43</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26湖产03</t>
+          <t>26凯利建设PPN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+2.00Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7227</t>
+          <t>2.3845</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6800</t>
+          <t>--/2.3500</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>湖州市产业投资发展集团有限公司</t>
+          <t>资阳市凯利建设投资有限责任公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C 26.74</t>
+          <t>C- 17.87</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4396,7 +4442,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4405,38 +4451,40 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V19" s="3"/>
+        <v>1.73</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.36%~2.46%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>四川省-资阳市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行拟募集资金5亿元,所募集资金拟用于偿还接续“25湖州产投SCP006”本金的过桥贷款[25湖州产投SCP006]</t>
+          <t>本期发行金额7.50亿元,拟用于偿还发行人存量债务融资工具本金[23凯利建设PPN002]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,江苏银行股份有限公司,东方证券股份有限公司,杭州银行股份有限公司,中信建投证券股份有限公司,徽商银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4457,7 +4505,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>湖州市产业投资发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>资阳市凯利建设投资有限责任公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4488,37 +4536,37 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
         <is>
-          <t>2029-10-22</t>
+          <t/>
         </is>
       </c>
       <c r="AV19" s="3" t="inlineStr">
@@ -4528,7 +4576,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4546,7 +4594,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26凯利建设PPN002</t>
+          <t>26滁州同创PPN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4557,53 +4605,57 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>43.47</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26凯利建设PPN001</t>
+          <t>24滁同01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2.3845</t>
+          <t>1.7478</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/2.3500</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>资阳市凯利建设投资有限责任公司</t>
+          <t>滁州市同创建设投资有限责任公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 17.87</t>
+          <t>C- 15.62</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4618,7 +4670,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4627,40 +4679,40 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.73</v>
+        <v>5.34</v>
       </c>
       <c r="V20" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2.36%~2.46%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>四川省-资阳市</t>
+          <t>安徽省-滁州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额7.50亿元,拟用于偿还发行人存量债务融资工具本金[23凯利建设PPN002]</t>
+          <t>本期发行金额为3.5亿元,计划将募集资金用于偿还债务融资工具本金[25滁州同创CP002,25滁州同创CP003]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
+          <t>中信银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4681,7 +4733,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>资阳市凯利建设投资有限责任公司2026年度第二期定向债务融资工具</t>
+          <t>滁州市同创建设投资有限责任公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4691,7 +4743,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-10-22</t>
+          <t>2029-10-22</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4712,12 +4764,12 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
@@ -4727,12 +4779,12 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
@@ -4765,69 +4817,79 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26滁州同创PPN002</t>
+          <t>G北清D1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>10-21 18:00</t>
-        </is>
-      </c>
-      <c r="C21" s="3"/>
+          <t>10-21 19:00</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>284306.SH</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>1.40 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>35.07</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>24滁同01</t>
+          <t>26北清电力SCP001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>219D</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7478</t>
+          <t>1.5368</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>滁州市同创建设投资有限责任公司</t>
+          <t>天津北清电力智慧能源有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 15.62</t>
+          <t>D 4.17</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4837,12 +4899,12 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-21 09:00</t>
+          <t>10-21 15:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4850,22 +4912,14 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U21" s="4" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t>1.76%~1.86%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X21" s="3"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4874,23 +4928,23 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>安徽省-滁州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为3.5亿元,计划将募集资金用于偿还债务融资工具本金[25滁州同创CP002,25滁州同创CP003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换本期债券发行前12个月内用于偿还绿色项目有息债务的自有资金支出</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,交通银行股份有限公司</t>
+          <t>国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4900,12 +4954,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>滁州市同创建设投资有限责任公司2026年度第二期定向债务融资工具</t>
+          <t>天津北清电力智慧能源有限公司2026年面向专业投资者非公开发行短期绿色公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4915,18 +4969,18 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-10-22</t>
+          <t>2027-10-22</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t/>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN21" s="3" t="inlineStr">
@@ -4936,32 +4990,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4989,14 +5043,12 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>G北清D1</t>
+          <t>26北控K6</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5006,58 +5058,62 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>284306.SH</t>
+          <t>246233.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.5</v>
+        <v>10.0</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>15.88</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26北清电力SCP001</t>
+          <t>26北控K4</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>219D</t>
+          <t>9.64Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.5368</t>
+          <t>1.8287</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>天津北清电力智慧能源有限公司</t>
+          <t>北京控股集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>D 4.17</t>
+          <t>C+ 31.39</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5077,36 +5133,46 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="U22" s="3"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>4.85</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X22" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.86%~1.96%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z22" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换本期债券发行前12个月内用于偿还绿色项目有息债务的自有资金支出</t>
+          <t>本期债券发行金额为不超过人民币20亿元,募集资金拟全部用于生产性支出,包括偿还债务、补充流动资金等。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,第一创业证券承销保荐有限责任公司,光大证券股份有限公司,招商证券股份有限公司,华泰联合证券有限责任公司,首创证券股份有限公司,申万宏源证券有限公司,北京证券有限责任公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5127,17 +5193,17 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>天津北清电力智慧能源有限公司2026年面向专业投资者非公开发行短期绿色公司债券(第一期)</t>
+          <t>北京控股集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2027-10-22</t>
+          <t>2036-10-23</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5153,17 +5219,17 @@
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
@@ -5173,17 +5239,17 @@
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5216,7 +5282,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26北控K6</t>
+          <t>26北控K5</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5226,12 +5292,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>246233.SH</t>
+          <t>246232.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -5240,34 +5306,38 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+          <t>1.20 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>15.47</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26北控K4</t>
+          <t>26北控集MTN005</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>9.64Y</t>
+          <t>2.69Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.8287</t>
+          <t>1.5630</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5300,7 +5370,9 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
+      <c r="U23" s="4" t="n">
+        <v>5.03</v>
+      </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
@@ -5309,7 +5381,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.52%~1.62%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5355,7 +5427,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>北京控股集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种二)</t>
+          <t>北京控股集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5365,7 +5437,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2036-10-23</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5444,7 +5516,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26北控K5</t>
+          <t>26南租K1</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5454,58 +5526,62 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>246232.SH</t>
+          <t>246216.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>1.20 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>17.03</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26北控集MTN005</t>
+          <t>26南航租赁SCP005</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.69Y</t>
+          <t>191D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5630</t>
+          <t>1.5090</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>北京控股集团有限公司</t>
+          <t>南航国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.39</t>
+          <t>C+ 31.51</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5515,7 +5591,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-21 15:00</t>
+          <t>10-21 16:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5525,19 +5601,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.62%</t>
+          <t>1.55%~1.65%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5552,17 +5628,17 @@
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过人民币20亿元,募集资金拟全部用于生产性支出,包括偿还债务、补充流动资金等。</t>
+          <t>本期债券募集资金2亿元,本期债券募集资金扣除发行费用后,拟将1.40亿元用于科创领域资产收购或置换前期科创领域资产收购所使用的自有资金,剩余部分用于偿还公司有息负债。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,第一创业证券承销保荐有限责任公司,光大证券股份有限公司,招商证券股份有限公司,华泰联合证券有限责任公司,首创证券股份有限公司,申万宏源证券有限公司,北京证券有限责任公司</t>
+          <t>中信建投证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5573,7 +5649,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5583,7 +5659,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>北京控股集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)(品种一)</t>
+          <t>南航国际融资租赁有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5593,10 +5669,14 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2028-10-22</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5604,42 +5684,42 @@
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5672,7 +5752,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26南租K1</t>
+          <t>26东吴07</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5682,94 +5762,96 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>246216.SH</t>
+          <t>246236.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.03</v>
+        <v>31.47</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>26东吴05</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>2.81Y</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>1.5791</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>1.5800/--</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.49</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>10-21 15:00</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>26南航租赁SCP005</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>191D</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>1.5090</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>1.5300/--</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>南航国际融资租赁有限公司</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>C+ 31.51</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>10-21 16:00</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="U25" s="3"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>4.59</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.65%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5784,28 +5866,28 @@
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金2亿元,本期债券募集资金扣除发行费用后,拟将1.40亿元用于科创领域资产收购或置换前期科创领域资产收购所使用的自有资金,剩余部分用于偿还公司有息负债。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还即将到期的公司债券本金(含置换偿还公司债券的自有资金)和补充流动资金。[25东吴04]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,广发证券股份有限公司</t>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5815,7 +5897,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>南航国际融资租赁有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>东吴证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5825,14 +5907,10 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2028-10-22</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-23</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5840,12 +5918,12 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
@@ -5855,7 +5933,7 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -5865,17 +5943,17 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5908,7 +5986,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26东吴07</t>
+          <t>26东吴08</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5918,12 +5996,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>246236.SH</t>
+          <t>246237.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -5932,38 +6010,38 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>31.47</v>
+        <v>32.43</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26东吴05</t>
+          <t>26东吴06</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.81Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5791</t>
+          <t>1.6702</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -5996,7 +6074,9 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U26" s="3"/>
+      <c r="U26" s="4" t="n">
+        <v>3.88</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
@@ -6005,7 +6085,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6051,7 +6131,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种一)</t>
+          <t>东吴证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6061,7 +6141,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2031-10-23</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6140,7 +6220,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26东吴08</t>
+          <t>26铁五Y1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6150,62 +6230,62 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>246237.SH</t>
+          <t>246261.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>32.43</v>
+        <v>59.43</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26东吴06</t>
+          <t>26铁四Y1</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.81Y</t>
+          <t>4.92Y+N</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6702</t>
+          <t>1.8259</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/1.8400</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中铁五局集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 40.49</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6215,7 +6295,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-21 15:00</t>
+          <t>10-21 16:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6232,12 +6312,12 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6252,28 +6332,28 @@
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还即将到期的公司债券本金(含置换偿还公司债券的自有资金)和补充流动资金。[25东吴04]</t>
+          <t>本期债券发行规模不超过10亿元(含10亿元),本期债券募集资金扣除发行费用后,拟用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中泰证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
@@ -6283,7 +6363,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
+          <t>中铁五局集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6314,32 +6394,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6354,12 +6434,12 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY27" s="3" t="inlineStr">
@@ -6372,7 +6452,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26铁五Y1</t>
+          <t>26海国10</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6382,62 +6462,62 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>246261.SH</t>
+          <t>246150.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>9.5</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>59.43</v>
+        <v>55.88</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26铁四Y1</t>
+          <t>26海国08</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.92Y+N</t>
+          <t>9.84Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.8259</t>
+          <t>2.2201</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.8600/1.8400</t>
+          <t>2.2500/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中铁五局集团有限公司</t>
+          <t>北京市海淀区国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C+ 30.18</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6464,12 +6544,12 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>2.28%~2.38%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6484,17 +6564,17 @@
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>北京市-海淀区</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过10亿元(含10亿元),本期债券募集资金扣除发行费用后,拟用于偿还有息债务。</t>
+          <t>本期债券发行金额为不超过19亿元(含19亿元)。本期公司债券募集资金拟全部用于偿还到期公募公司债券本金。[23海国07]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6505,7 +6585,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6515,7 +6595,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中铁五局集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>北京市海淀区国有资本运营有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6525,7 +6605,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
+          <t>2036-10-23</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6546,7 +6626,7 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6556,22 +6636,22 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6586,12 +6666,12 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY28" s="3" t="inlineStr">
@@ -6604,7 +6684,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26海国10</t>
+          <t>26开投Y1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6614,47 +6694,47 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>246150.SH</t>
+          <t>520540.SZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>55.88</v>
+        <v>74.43</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26海国08</t>
+          <t>25开投Y1</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>9.84Y</t>
+          <t>2.02Y+N</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.2201</t>
+          <t>2.0966</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6664,12 +6744,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区国有资本运营有限公司</t>
+          <t>开封国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.18</t>
+          <t>C+ 31.64</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6679,7 +6759,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-21 16:00</t>
+          <t>10-21 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6689,44 +6769,40 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.28%~2.38%</t>
+          <t>2.23%~2.33%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>北京市-海淀区</t>
+          <t>河南省-开封市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过19亿元(含19亿元)。本期公司债券募集资金拟全部用于偿还到期公募公司债券本金。[23海国07]</t>
+          <t>本期债券募集资金规模为不超过人民币2.40亿元(含2.40亿元),扣除发行费用后拟全部用于偿还“23开投05”公司债券本金。[23开投05]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,中信证券股份有限公司</t>
+          <t>西部证券股份有限公司,中信证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6742,22 +6818,22 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区国有资本运营有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
+          <t>开封国有资产投资经营集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2036-10-23</t>
+          <t>2031-10-22</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6768,44 +6844,32 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ29" s="3" t="inlineStr">
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="3"/>
+      <c r="AS29" s="3"/>
+      <c r="AT29" s="3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR29" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6818,12 +6882,12 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY29" s="3" t="inlineStr">
@@ -6836,7 +6900,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26开投Y1</t>
+          <t>26白银01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6846,62 +6910,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>520540.SZ</t>
+          <t>520522.SZ</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.4</v>
+        <v>5.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.70 ~ 2.30</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>74.43</v>
+        <v>52.47</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25开投Y1</t>
+          <t>26湖南白银MTN001(科创债)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.02Y+N</t>
+          <t>2.83Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.0966</t>
+          <t>1.7364</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>2.2500/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>开封国有资产投资经营集团有限公司</t>
+          <t>湖南白银股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.64</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6921,19 +6985,21 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="U30" s="3"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>2.27</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.23%~2.33%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6944,17 +7010,17 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>河南省-开封市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金规模为不超过人民币2.40亿元(含2.40亿元),扣除发行费用后拟全部用于偿还“23开投05”公司债券本金。[23开投05]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还有息债务;在相关有息债务偿付日前,可在不影响偿债计划的前提下,将闲置募集资金临时用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司,中信证券股份有限公司,兴业证券股份有限公司</t>
+          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -6975,7 +7041,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>开封国有资产投资经营集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>湖南白银股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6985,7 +7051,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-22</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7001,25 +7067,37 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3"/>
-      <c r="AR30" s="3"/>
-      <c r="AS30" s="3"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>贵金属</t>
+        </is>
+      </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>稀有金属</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7034,12 +7112,12 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY30" s="3" t="inlineStr">
@@ -7052,7 +7130,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26白银01</t>
+          <t>26财通C4</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7062,7 +7140,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>520522.SZ</t>
+          <t>246248.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -7071,53 +7149,53 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>52.47</v>
+        <v>35.47</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26湖南白银MTN001(科创债)</t>
+          <t>24财通C5</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.83Y</t>
+          <t>2.80Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7364</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>1.5700/1.5400</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>湖南白银股份有限公司</t>
+          <t>财通证券股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>B- 42.30</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7144,39 +7222,43 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z31" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还有息债务;在相关有息债务偿付日前,可在不影响偿债计划的前提下,将闲置募集资金临时用于补充流动资金。</t>
+          <t>本期债券的募集资金扣除发行费用后,拟用于置换已用于偿还公司债券本金的自有资金。[23财通F3]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司次级债</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7186,17 +7268,17 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>湖南白银股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>财通证券股份有限公司2026年面向专业投资者公开发行次级债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
@@ -7212,7 +7294,7 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7222,32 +7304,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>贵金属</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>稀有金属</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7267,7 +7349,7 @@
       </c>
       <c r="AX31" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY31" s="3" t="inlineStr">
@@ -7280,7 +7362,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26财通C4</t>
+          <t>26财通C5</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7290,12 +7372,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>246248.SH</t>
+          <t>246249.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7304,38 +7386,38 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>35.47</v>
+        <v>36.43</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24财通C5</t>
+          <t>26财通C3</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.80Y</t>
+          <t>4.73Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7157</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.5700/1.5400</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -7377,7 +7459,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7423,7 +7505,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司2026年面向专业投资者公开发行次级债券(第三期)(品种一)</t>
+          <t>财通证券股份有限公司2026年面向专业投资者公开发行次级债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7433,7 +7515,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2031-10-23</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7512,7 +7594,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26财通C5</t>
+          <t>26深投11(取消发行)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7522,7 +7604,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>246249.SH</t>
+          <t>DY525051.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7531,20 +7613,16 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>36.43</v>
-      </c>
+          <t>1.40 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -7552,32 +7630,32 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26财通C3</t>
+          <t>26深投09</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.73Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7157</t>
+          <t>1.6451</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>1.6500/1.6300</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 42.30</t>
+          <t>C+ 33.86</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7597,19 +7675,19 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7624,23 +7702,23 @@
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,拟用于置换已用于偿还公司债券本金的自有资金。[23财通F3]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[21深投06]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>证券公司次级债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7650,12 +7728,12 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司2026年面向专业投资者公开发行次级债券(第三期)(品种二)</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第六期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7665,10 +7743,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2031-10-26</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7676,42 +7758,42 @@
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7731,7 +7813,7 @@
       </c>
       <c r="AX33" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY33" s="3" t="inlineStr">
@@ -7744,68 +7826,74 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26深投11(取消发行)</t>
+          <t>26海南农垦SCP002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-21 19:00</t>
+          <t>10-21 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>DY525051.SZ</t>
+          <t>012682503.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+          <t>1.42 ~ 1.72</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>30.96</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26深投09</t>
+          <t>22海垦01</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6451</t>
+          <t>1.4950</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.6500/1.6300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>海南省农垦投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.86</t>
+          <t>C+ 30.98</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7815,29 +7903,33 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-21 15:00</t>
+          <t>10-21 10:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>2.75</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7845,30 +7937,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>海南省-海口市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[21深投06]</t>
+          <t>本期拟发行10亿元人民币,8.4亿元用于归还发行人到期债务,1.6亿元用于补充母公司或子公司流动资金。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7878,12 +7966,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第六期)(品种一)(取消发行)</t>
+          <t>海南省农垦投资控股集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7893,64 +7981,60 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-10-26</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-19</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7971,7 +8055,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AZ34" s="3"/>
+      <c r="AZ34" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
@@ -8467,8 +8553,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="H37" s="4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>56.88</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>2.03</t>
@@ -8701,8 +8791,12 @@
           <t>1.10 ~ 1.41</t>
         </is>
       </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="H38" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>21.19</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
           <t>1.31</t>
@@ -8929,8 +9023,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="H39" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>32.43</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -8987,7 +9085,7 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>5.255</v>
+        <v>5.26</v>
       </c>
       <c r="V39" s="4" t="n">
         <v>1.25</v>
@@ -9159,8 +9257,12 @@
           <t>1.70 ~ 1.90</t>
         </is>
       </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+      <c r="H40" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>18.88</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
           <t>1.89</t>
@@ -9220,7 +9322,7 @@
         <v>2.38</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>1.175</v>
+        <v>1.18</v>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
@@ -9393,8 +9495,12 @@
           <t>1.50 ~ 1.90</t>
         </is>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+      <c r="H41" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>27.43</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>1.74</t>
@@ -9645,7 +9751,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/1.6000</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -9847,8 +9953,12 @@
           <t>1.45 ~ 2.05</t>
         </is>
       </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+      <c r="H43" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>33.03</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -10083,8 +10193,12 @@
           <t>1.70 ~ 2.20</t>
         </is>
       </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="H44" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>63.47</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>1.97</t>
@@ -10313,8 +10427,12 @@
           <t>1.30 ~ 1.90</t>
         </is>
       </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+      <c r="H45" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>32.86</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>1.50</t>
@@ -10543,8 +10661,12 @@
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+      <c r="H46" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>40.47</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -11001,8 +11123,12 @@
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="H48" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>43.47</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -11058,8 +11184,12 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
+      <c r="U48" s="4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>1.83</v>
+      </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -11247,7 +11377,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -11449,8 +11579,12 @@
           <t>1.50 ~ 1.90</t>
         </is>
       </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="H50" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>27.43</v>
+      </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
           <t>1.74</t>
@@ -11507,7 +11641,7 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>4.125</v>
+        <v>4.13</v>
       </c>
       <c r="V50" s="4" t="n">
         <v>1.0</v>
@@ -11679,8 +11813,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="H51" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>19.43</v>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>1.61</t>
@@ -11933,7 +12071,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -12135,8 +12273,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="H53" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>37.07</v>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
           <t>1.61</t>
@@ -12365,8 +12507,12 @@
           <t>1.60 ~ 2.06</t>
         </is>
       </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+      <c r="H54" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>34.88</v>
+      </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
           <t>1.96</t>
@@ -12646,7 +12792,7 @@
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
@@ -12655,10 +12801,10 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>4.0</v>
+        <v>4.99</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>3.9</v>
+        <v>2.41</v>
       </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
@@ -12878,7 +13024,7 @@
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr">
@@ -12888,7 +13034,7 @@
       </c>
       <c r="U56" s="3"/>
       <c r="V56" s="4" t="n">
-        <v>1.2</v>
+        <v>1.0</v>
       </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
@@ -13023,7 +13169,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ56" s="3"/>
+      <c r="AZ56" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
@@ -13057,8 +13205,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+      <c r="H57" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>22.0</v>
+      </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>1.45</t>
@@ -13114,7 +13266,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U57" s="3"/>
+      <c r="U57" s="4" t="n">
+        <v>2.26</v>
+      </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
@@ -13285,8 +13439,12 @@
           <t>1.50 ~ 1.90</t>
         </is>
       </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+      <c r="H58" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>29.47</v>
+      </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
           <t>1.59</t>
@@ -13515,8 +13673,12 @@
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+      <c r="H59" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>36.43</v>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
@@ -13749,8 +13911,12 @@
           <t>1.20 ~ 1.80</t>
         </is>
       </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="H60" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>19.07</v>
+      </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -13979,8 +14145,12 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="H61" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>29.03</v>
+      </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
           <t>1.51</t>
@@ -14209,8 +14379,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="H62" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>49.47</v>
+      </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -14437,8 +14611,12 @@
           <t>1.70 ~ 1.99</t>
         </is>
       </c>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="H63" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>34.88</v>
+      </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
           <t>1.99</t>
@@ -14495,7 +14673,7 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>1.125</v>
+        <v>1.13</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
@@ -14667,8 +14845,12 @@
           <t>1.44 ~ 1.74</t>
         </is>
       </c>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="H64" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>22.47</v>
+      </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
           <t>1.59</t>
@@ -14724,7 +14906,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U64" s="3"/>
+      <c r="U64" s="4" t="n">
+        <v>2.49</v>
+      </c>
       <c r="V64" s="4" t="n">
         <v>1.22</v>
       </c>
@@ -14895,8 +15079,12 @@
           <t>1.50 ~ 2.20</t>
         </is>
       </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="H65" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>43.47</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -15127,8 +15315,12 @@
           <t>1.55 ~ 1.75</t>
         </is>
       </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="H66" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>57.07</v>
+      </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -15355,8 +15547,12 @@
           <t>5.21 ~ 6.21</t>
         </is>
       </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="H67" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>484.96</v>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>6.20</t>
@@ -15581,8 +15777,12 @@
           <t>1.80 ~ 2.20</t>
         </is>
       </c>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
+      <c r="H68" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>8.76</v>
+      </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
           <t>2.02</t>
@@ -16039,8 +16239,12 @@
           <t>1.20 ~ 1.60</t>
         </is>
       </c>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="H70" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>14.03</v>
+      </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
           <t>1.54</t>
@@ -16271,8 +16475,12 @@
           <t>1.50 ~ 2.10</t>
         </is>
       </c>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="H71" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>28.43</v>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>1.73</t>
@@ -16503,8 +16711,12 @@
           <t>1.20 ~ 1.60</t>
         </is>
       </c>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="H72" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>19.96</v>
+      </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
           <t>1.37</t>
@@ -16733,8 +16945,12 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+      <c r="H73" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>63.43</v>
+      </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
           <t>2.02</t>
@@ -17185,8 +17401,12 @@
           <t>1.45 ~ 1.95</t>
         </is>
       </c>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+      <c r="H75" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>42.03</v>
+      </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
@@ -17243,10 +17463,10 @@
         </is>
       </c>
       <c r="U75" s="4" t="n">
-        <v>2.6147</v>
+        <v>2.61</v>
       </c>
       <c r="V75" s="4" t="n">
-        <v>1.1417</v>
+        <v>1.14</v>
       </c>
       <c r="W75" s="3" t="inlineStr">
         <is>
@@ -17419,8 +17639,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
+      <c r="H76" s="4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>97.43</v>
+      </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
           <t>2.32</t>
@@ -17647,8 +17871,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="H77" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>55.88</v>
+      </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
           <t>2.26</t>
@@ -17711,7 +17939,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="X77" s="3"/>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>2.09%~2.19%</t>
+        </is>
+      </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -18109,8 +18341,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+      <c r="H79" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>45.47</v>
+      </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -18394,7 +18630,9 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U80" s="3"/>
+      <c r="U80" s="4" t="n">
+        <v>2.48</v>
+      </c>
       <c r="V80" s="3"/>
       <c r="W80" s="3" t="inlineStr">
         <is>
@@ -19310,7 +19548,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U84" s="3"/>
+      <c r="U84" s="4" t="n">
+        <v>2.39</v>
+      </c>
       <c r="V84" s="3"/>
       <c r="W84" s="3" t="inlineStr">
         <is>
@@ -19994,7 +20234,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U87" s="3"/>
+      <c r="U87" s="4" t="n">
+        <v>4.53</v>
+      </c>
       <c r="V87" s="3"/>
       <c r="W87" s="3" t="inlineStr">
         <is>
@@ -20674,7 +20916,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U90" s="3"/>
+      <c r="U90" s="4" t="n">
+        <v>7.06</v>
+      </c>
       <c r="V90" s="3"/>
       <c r="W90" s="3" t="inlineStr">
         <is>
@@ -20902,7 +21146,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U91" s="3"/>
+      <c r="U91" s="4" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V91" s="3"/>
       <c r="W91" s="3" t="inlineStr">
         <is>
